--- a/04-exam-1/Exam 1 Quiz and Item Analysis Report.xlsx
+++ b/04-exam-1/Exam 1 Quiz and Item Analysis Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onis0001\Documents\GitHub\HES-3000-Sports-Data-Analytics\04-exam-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saryu/Documents/GitHub/HES-3000-Sports-Performance-Analytics/04-exam-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201E8085-18F4-4E00-966C-891DD82318D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45857498-BB63-E447-9CC7-19FF4990C76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1515" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{39CFC490-CD87-4991-A730-77AE5E125ABB}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="24320" windowHeight="18380" activeTab="1" xr2:uid="{39CFC490-CD87-4991-A730-77AE5E125ABB}"/>
   </bookViews>
   <sheets>
     <sheet name="Exam 1 Quiz and Item Analysis R" sheetId="1" r:id="rId1"/>
@@ -1036,12 +1036,8 @@
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1090,7 +1086,7 @@
   <dxfs count="4">
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
@@ -1456,9 +1452,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B814FE5B-29C6-4E37-9BFC-632C3566FAAA}">
   <dimension ref="A1:W41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1558,7 +1554,7 @@
         <v>3.3425925925925928E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J3">
         <v>353182</v>
       </c>
@@ -1602,7 +1598,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J4">
         <v>353178</v>
       </c>
@@ -1646,7 +1642,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J5">
         <v>353197</v>
       </c>
@@ -1690,7 +1686,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J6">
         <v>353203</v>
       </c>
@@ -1734,7 +1730,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J7">
         <v>353193</v>
       </c>
@@ -1778,7 +1774,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J8">
         <v>353176</v>
       </c>
@@ -1822,7 +1818,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J9">
         <v>353218</v>
       </c>
@@ -1866,7 +1862,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J10">
         <v>353208</v>
       </c>
@@ -1910,7 +1906,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J11">
         <v>405565</v>
       </c>
@@ -1954,7 +1950,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J12">
         <v>353184</v>
       </c>
@@ -1998,7 +1994,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J13">
         <v>353219</v>
       </c>
@@ -2042,7 +2038,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J14">
         <v>353186</v>
       </c>
@@ -2086,7 +2082,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J15">
         <v>353221</v>
       </c>
@@ -2130,7 +2126,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="J16">
         <v>353211</v>
       </c>
@@ -2174,7 +2170,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J17">
         <v>353201</v>
       </c>
@@ -2218,7 +2214,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J18">
         <v>353199</v>
       </c>
@@ -2262,7 +2258,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J19">
         <v>353174</v>
       </c>
@@ -2306,7 +2302,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J20">
         <v>353223</v>
       </c>
@@ -2350,7 +2346,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J21">
         <v>353229</v>
       </c>
@@ -2394,7 +2390,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J22">
         <v>353232</v>
       </c>
@@ -2438,7 +2434,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J23">
         <v>353225</v>
       </c>
@@ -2482,7 +2478,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J24">
         <v>405014</v>
       </c>
@@ -2526,7 +2522,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J25">
         <v>353228</v>
       </c>
@@ -2570,7 +2566,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J26">
         <v>405013</v>
       </c>
@@ -2614,7 +2610,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J27">
         <v>405566</v>
       </c>
@@ -2658,7 +2654,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J28">
         <v>353234</v>
       </c>
@@ -2702,7 +2698,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J29">
         <v>353233</v>
       </c>
@@ -2746,7 +2742,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="30" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J30">
         <v>353231</v>
       </c>
@@ -2790,7 +2786,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="31" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J31">
         <v>353215</v>
       </c>
@@ -2834,7 +2830,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J32">
         <v>353190</v>
       </c>
@@ -2878,7 +2874,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J33">
         <v>353227</v>
       </c>
@@ -2922,7 +2918,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J34">
         <v>353217</v>
       </c>
@@ -2966,7 +2962,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="35" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J35">
         <v>353230</v>
       </c>
@@ -3010,7 +3006,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J36">
         <v>353222</v>
       </c>
@@ -3054,7 +3050,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J37">
         <v>353213</v>
       </c>
@@ -3098,7 +3094,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J38">
         <v>353188</v>
       </c>
@@ -3142,7 +3138,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="39" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J39">
         <v>405012</v>
       </c>
@@ -3186,7 +3182,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J40">
         <v>353220</v>
       </c>
@@ -3230,7 +3226,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="41" spans="10:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="10:23" x14ac:dyDescent="0.2">
       <c r="J41">
         <v>353195</v>
       </c>
@@ -3282,19 +3278,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C92D560-9D70-40EA-B3FE-37917B00CA15}">
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="105.28515625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" customWidth="1"/>
+    <col min="7" max="7" width="105.33203125" style="5" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -3320,7 +3316,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>353233</v>
       </c>
@@ -3348,7 +3344,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>353234</v>
       </c>
@@ -3376,7 +3372,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>353232</v>
       </c>
@@ -3404,7 +3400,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>353178</v>
       </c>
@@ -3432,7 +3428,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>353229</v>
       </c>
@@ -3460,7 +3456,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>353231</v>
       </c>
@@ -3488,7 +3484,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>405014</v>
       </c>
@@ -3516,7 +3512,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>353195</v>
       </c>
@@ -3544,7 +3540,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>353190</v>
       </c>
@@ -3572,7 +3568,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>353182</v>
       </c>
@@ -3600,7 +3596,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>405012</v>
       </c>
@@ -3628,7 +3624,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>353193</v>
       </c>
@@ -3654,7 +3650,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>353208</v>
       </c>
@@ -3680,7 +3676,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>353201</v>
       </c>
@@ -3706,7 +3702,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>353197</v>
       </c>
@@ -3732,7 +3728,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>353211</v>
       </c>
@@ -3758,7 +3754,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>353222</v>
       </c>
@@ -3784,7 +3780,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>353203</v>
       </c>
@@ -3810,7 +3806,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>353223</v>
       </c>
@@ -3836,7 +3832,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>353227</v>
       </c>
@@ -3862,7 +3858,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>353228</v>
       </c>
@@ -3888,7 +3884,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>353188</v>
       </c>
@@ -3914,7 +3910,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>353199</v>
       </c>
@@ -3940,7 +3936,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>353219</v>
       </c>
@@ -3966,7 +3962,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>353220</v>
       </c>
@@ -3992,7 +3988,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>353225</v>
       </c>
@@ -4018,7 +4014,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>353230</v>
       </c>
@@ -4044,7 +4040,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>353184</v>
       </c>
@@ -4070,7 +4066,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>353215</v>
       </c>
@@ -4096,7 +4092,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>353174</v>
       </c>
@@ -4122,7 +4118,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>353186</v>
       </c>
@@ -4148,7 +4144,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>405013</v>
       </c>
@@ -4174,7 +4170,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>405566</v>
       </c>
@@ -4200,7 +4196,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>353217</v>
       </c>
@@ -4226,7 +4222,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>353218</v>
       </c>
@@ -4252,7 +4248,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>353176</v>
       </c>
@@ -4278,7 +4274,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>353213</v>
       </c>
@@ -4304,7 +4300,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>353221</v>
       </c>
@@ -4330,7 +4326,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>405565</v>
       </c>
